--- a/templates/마케팅-대시보드-입력.xlsx
+++ b/templates/마케팅-대시보드-입력.xlsx
@@ -6,11 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="안내" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="매체_수동" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="플레이스_순위" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="플레이스_지표" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="바이럴" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="SNS" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="목록" state="visible" r:id="rId10"/>
+    <sheet sheetId="3" name="목록" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -46,23 +42,6 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <t>순위권 밖이면 비움</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
     <comment ref="A1" authorId="0">
       <text>
         <r>
@@ -75,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>마케팅 대시보드 입력</t>
   </si>
@@ -143,42 +122,12 @@
     <t>API 가 없는 매체의 주간 성과. 매주 월요일에 지난주 숫자를 채널(·세그먼트)마다 한 줄씩</t>
   </si>
   <si>
-    <t>플레이스_순위</t>
-  </si>
-  <si>
-    <t>네이버 플레이스 키워드 순위. 매주 같은 요일에 키워드마다 한 줄</t>
-  </si>
-  <si>
-    <t>플레이스_지표</t>
-  </si>
-  <si>
-    <t>스마트플레이스의 리뷰 수·평점·저장 수(누적값). 매주 한 줄</t>
-  </si>
-  <si>
-    <t>바이럴</t>
-  </si>
-  <si>
-    <t>블로그·카페 글을 발행할 때마다 한 줄. 상위노출은 확인할 때 O/X 갱신</t>
-  </si>
-  <si>
-    <t>SNS</t>
-  </si>
-  <si>
-    <t>SNS 팔로워(주 마지막 날 기준)와 그 주 조회수. 인스타그램 API 연결 전까지</t>
-  </si>
-  <si>
     <t>예시 (매체_수동)</t>
   </si>
   <si>
     <t>2026-10-19 | GU강남 | 강남언니 | (비움) | 1100000 | 78500 | 1890 | 170</t>
   </si>
   <si>
-    <t>예시 (바이럴)</t>
-  </si>
-  <si>
-    <t>2026-10-21 | GU일산 | 블로그 | https://blog.naver.com/... | 일산 여드름 | O | 2026-10-24</t>
-  </si>
-  <si>
     <t>주 시작일(월)</t>
   </si>
   <si>
@@ -194,7 +143,7 @@
     <t>소진액(원)</t>
   </si>
   <si>
-    <t>노출(문자는 발송 수)</t>
+    <t>노출</t>
   </si>
   <si>
     <t>클릭</t>
@@ -206,103 +155,25 @@
     <t>메모</t>
   </si>
   <si>
-    <t>키워드</t>
-  </si>
-  <si>
-    <t>순위</t>
-  </si>
-  <si>
-    <t>리뷰 수</t>
-  </si>
-  <si>
-    <t>평점</t>
-  </si>
-  <si>
-    <t>저장 수</t>
-  </si>
-  <si>
-    <t>발행일</t>
-  </si>
-  <si>
-    <t>플랫폼</t>
-  </si>
-  <si>
-    <t>글 주소</t>
-  </si>
-  <si>
-    <t>목표 키워드</t>
-  </si>
-  <si>
-    <t>상위노출</t>
-  </si>
-  <si>
-    <t>확인일</t>
-  </si>
-  <si>
-    <t>팔로워</t>
-  </si>
-  <si>
-    <t>조회수</t>
-  </si>
-  <si>
     <t>채널(수기)</t>
   </si>
   <si>
-    <t>SNS 플랫폼</t>
-  </si>
-  <si>
-    <t>바이럴 플랫폼</t>
-  </si>
-  <si>
     <t>GU강남</t>
   </si>
   <si>
     <t>강남언니</t>
   </si>
   <si>
-    <t>인스타그램</t>
-  </si>
-  <si>
-    <t>블로그</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
     <t>GU일산</t>
   </si>
   <si>
     <t>크리에이트립</t>
   </si>
   <si>
-    <t>유튜브</t>
-  </si>
-  <si>
-    <t>카페</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>루호</t>
   </si>
   <si>
     <t>당근</t>
-  </si>
-  <si>
-    <t>틱톡</t>
-  </si>
-  <si>
-    <t>지식인</t>
-  </si>
-  <si>
-    <t>셀로라</t>
-  </si>
-  <si>
-    <t>카톡·문자</t>
-  </si>
-  <si>
-    <t>기타</t>
   </si>
 </sst>
 </file>
@@ -358,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -382,13 +253,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -731,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
@@ -844,58 +708,18 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -913,38 +737,37 @@
     <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20" style="5" customWidth="1"/>
-    <col min="7" max="8" width="12" style="5" customWidth="1"/>
+    <col min="6" max="8" width="12" style="5" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -954,10 +777,10 @@
       <formula1>AND(ISNUMBER(A2),WEEKDAY(A2,2)=1)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="B2:B1001">
-      <formula1>'목록'!$A$2:$A$5</formula1>
+      <formula1>'목록'!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="C2:C1001">
-      <formula1>'목록'!$B$2:$B$5</formula1>
+      <formula1>'목록'!$B$2:$B$4</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="E2:E1001">
       <formula1>0</formula1>
@@ -980,295 +803,42 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" style="5" customWidth="1"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D1"/>
-  <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="월요일 날짜(YYYY-MM-DD)를 적어 주세요" sqref="A2:A1001">
-      <formula1>AND(ISNUMBER(A2),WEEKDAY(A2,2)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="B2:B1001">
-      <formula1>'목록'!$A$2:$A$5</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="D2:D1001">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="18" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12" style="5" customWidth="1"/>
-    <col min="4" max="4" width="12" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E1"/>
-  <dataValidations count="5">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="월요일 날짜(YYYY-MM-DD)를 적어 주세요" sqref="A2:A1001">
-      <formula1>AND(ISNUMBER(A2),WEEKDAY(A2,2)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="B2:B1001">
-      <formula1>'목록'!$A$2:$A$5</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="C2:C1001">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0~5 사이 숫자를 적어 주세요" sqref="D2:D1001">
-      <formula1>0</formula1>
-      <formula2>5</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="E2:E1001">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" style="4" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12" style="4" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G1"/>
-  <dataValidations count="5">
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="날짜(YYYY-MM-DD)를 적어 주세요" sqref="A2:A1001">
-      <formula1>45291.625</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="B2:B1001">
-      <formula1>'목록'!$A$2:$A$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="C2:C1001">
-      <formula1>'목록'!$D$2:$D$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="F2:F1001">
-      <formula1>'목록'!$E$2:$E$3</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="날짜(YYYY-MM-DD)를 적어 주세요" sqref="G2:G1001">
-      <formula1>45291.625</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="18" style="4" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="5" width="12" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E1"/>
-  <dataValidations count="5">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="월요일 날짜(YYYY-MM-DD)를 적어 주세요" sqref="A2:A1001">
-      <formula1>AND(ISNUMBER(A2),WEEKDAY(A2,2)=1)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="B2:B1001">
-      <formula1>'목록'!$A$2:$A$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="목록에서 골라 주세요" sqref="C2:C1001">
-      <formula1>'목록'!$C$2:$C$4</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="D2:D1001">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" error="0 이상의 정수를 적어 주세요(콤마·₩ 없이)" sqref="E2:E1001">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="5" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
